--- a/diseases/d146/2010-2014.xlsx
+++ b/diseases/d146/2010-2014.xlsx
@@ -776,28 +776,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U2" t="inlineStr">
+        <is>
+          <t>HOLD_JP_0d0f562527f933882ae5ffa7bbb4</t>
+        </is>
+      </c>
+      <c r="AA2" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR2" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS2" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ2" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS2" t="inlineStr">
+        <is>
+          <t>HOLD_JP_0d0f562527f933882ae5ffa7bbb4</t>
+        </is>
+      </c>
       <c r="AT2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU2" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV2" t="inlineStr">
@@ -924,28 +938,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>HOLD_JP_0d0f562527f933882ae5ffa7bbb4</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR3" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS3" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ3" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS3" t="inlineStr">
+        <is>
+          <t>HOLD_JP_0d0f562527f933882ae5ffa7bbb4</t>
+        </is>
+      </c>
       <c r="AT3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU3" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV3" t="inlineStr">
@@ -1072,28 +1100,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>HOLD_JP_0d0f562527f933882ae5ffa7bbb4</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR4" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS4" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ4" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS4" t="inlineStr">
+        <is>
+          <t>HOLD_JP_0d0f562527f933882ae5ffa7bbb4</t>
+        </is>
+      </c>
       <c r="AT4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU4" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV4" t="inlineStr">
@@ -1220,28 +1262,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>HOLD_JP_0d0f562527f933882ae5ffa7bbb4</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR5" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS5" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ5" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS5" t="inlineStr">
+        <is>
+          <t>HOLD_JP_0d0f562527f933882ae5ffa7bbb4</t>
+        </is>
+      </c>
       <c r="AT5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU5" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV5" t="inlineStr">
@@ -1368,28 +1424,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>HOLD_JP_0d0f562527f933882ae5ffa7bbb4</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR6" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS6" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ6" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS6" t="inlineStr">
+        <is>
+          <t>HOLD_JP_0d0f562527f933882ae5ffa7bbb4</t>
+        </is>
+      </c>
       <c r="AT6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU6" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV6" t="inlineStr">
@@ -1516,28 +1586,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>HOLD_JP_0d0f562527f933882ae5ffa7bbb4</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR7" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS7" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ7" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS7" t="inlineStr">
+        <is>
+          <t>HOLD_JP_0d0f562527f933882ae5ffa7bbb4</t>
+        </is>
+      </c>
       <c r="AT7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU7" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV7" t="inlineStr">
@@ -1664,28 +1748,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>HOLD_JP_0d0f562527f933882ae5ffa7bbb4</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR8" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS8" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ8" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS8" t="inlineStr">
+        <is>
+          <t>HOLD_JP_0d0f562527f933882ae5ffa7bbb4</t>
+        </is>
+      </c>
       <c r="AT8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU8" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV8" t="inlineStr">
@@ -1812,28 +1910,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>HOLD_JP_0d0f562527f933882ae5ffa7bbb4</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR9" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS9" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ9" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS9" t="inlineStr">
+        <is>
+          <t>HOLD_JP_0d0f562527f933882ae5ffa7bbb4</t>
+        </is>
+      </c>
       <c r="AT9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU9" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV9" t="inlineStr">
@@ -1960,28 +2072,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>HOLD_JP_0d0f562527f933882ae5ffa7bbb4</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR10" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS10" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ10" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS10" t="inlineStr">
+        <is>
+          <t>HOLD_JP_0d0f562527f933882ae5ffa7bbb4</t>
+        </is>
+      </c>
       <c r="AT10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU10" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV10" t="inlineStr">
@@ -2108,28 +2234,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>HOLD_JP_0d0f562527f933882ae5ffa7bbb4</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR11" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS11" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ11" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS11" t="inlineStr">
+        <is>
+          <t>HOLD_JP_0d0f562527f933882ae5ffa7bbb4</t>
+        </is>
+      </c>
       <c r="AT11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU11" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV11" t="inlineStr">
@@ -2256,28 +2396,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>HOLD_JP_0d0f562527f933882ae5ffa7bbb4</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR12" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS12" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ12" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS12" t="inlineStr">
+        <is>
+          <t>HOLD_JP_0d0f562527f933882ae5ffa7bbb4</t>
+        </is>
+      </c>
       <c r="AT12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU12" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV12" t="inlineStr">
@@ -2404,28 +2558,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>HOLD_JP_0d0f562527f933882ae5ffa7bbb4</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO13" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP13" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR13" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS13" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ13" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS13" t="inlineStr">
+        <is>
+          <t>HOLD_JP_0d0f562527f933882ae5ffa7bbb4</t>
+        </is>
+      </c>
       <c r="AT13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU13" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV13" t="inlineStr">
@@ -2552,28 +2720,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>HOLD_JP_0d0f562527f933882ae5ffa7bbb4</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO14" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP14" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR14" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS14" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ14" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS14" t="inlineStr">
+        <is>
+          <t>HOLD_JP_0d0f562527f933882ae5ffa7bbb4</t>
+        </is>
+      </c>
       <c r="AT14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU14" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV14" t="inlineStr">
@@ -2700,28 +2882,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>HOLD_JP_0d0f562527f933882ae5ffa7bbb4</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO15" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP15" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR15" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS15" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ15" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS15" t="inlineStr">
+        <is>
+          <t>HOLD_JP_0d0f562527f933882ae5ffa7bbb4</t>
+        </is>
+      </c>
       <c r="AT15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU15" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV15" t="inlineStr">
@@ -2848,28 +3044,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>HOLD_JP_0d0f562527f933882ae5ffa7bbb4</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO16" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP16" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR16" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS16" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ16" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS16" t="inlineStr">
+        <is>
+          <t>HOLD_JP_0d0f562527f933882ae5ffa7bbb4</t>
+        </is>
+      </c>
       <c r="AT16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU16" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV16" t="inlineStr">

--- a/diseases/d146/2010-2014.xlsx
+++ b/diseases/d146/2010-2014.xlsx
@@ -765,17 +765,15 @@
       <c r="O2" t="n">
         <v>0</v>
       </c>
+      <c r="P2" t="n">
+        <v>0</v>
+      </c>
       <c r="Q2" t="n">
         <v>0</v>
       </c>
       <c r="R2" t="n">
         <v>0</v>
       </c>
-      <c r="S2" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U2" t="inlineStr">
         <is>
           <t>HOLD_JP_0d0f562527f933882ae5ffa7bbb4</t>
@@ -783,7 +781,7 @@
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO2" t="inlineStr">
@@ -793,12 +791,7 @@
       </c>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ2" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS2" t="inlineStr">
@@ -809,11 +802,6 @@
       <c r="AT2" t="n">
         <v>1</v>
       </c>
-      <c r="AU2" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
-      </c>
       <c r="AV2" t="inlineStr">
         <is>
           <t>jp_weekly</t>
@@ -927,17 +915,15 @@
       <c r="O3" t="n">
         <v>2</v>
       </c>
+      <c r="P3" t="n">
+        <v>2</v>
+      </c>
       <c r="Q3" t="n">
         <v>0</v>
       </c>
       <c r="R3" t="n">
         <v>0.001568792272603041</v>
       </c>
-      <c r="S3" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U3" t="inlineStr">
         <is>
           <t>HOLD_JP_0d0f562527f933882ae5ffa7bbb4</t>
@@ -945,7 +931,7 @@
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO3" t="inlineStr">
@@ -955,12 +941,7 @@
       </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ3" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS3" t="inlineStr">
@@ -971,11 +952,6 @@
       <c r="AT3" t="n">
         <v>1</v>
       </c>
-      <c r="AU3" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
-      </c>
       <c r="AV3" t="inlineStr">
         <is>
           <t>jp_weekly</t>
@@ -1089,17 +1065,15 @@
       <c r="O4" t="n">
         <v>0</v>
       </c>
+      <c r="P4" t="n">
+        <v>0</v>
+      </c>
       <c r="Q4" t="n">
         <v>0</v>
       </c>
       <c r="R4" t="n">
         <v>0</v>
       </c>
-      <c r="S4" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U4" t="inlineStr">
         <is>
           <t>HOLD_JP_0d0f562527f933882ae5ffa7bbb4</t>
@@ -1107,7 +1081,7 @@
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO4" t="inlineStr">
@@ -1117,12 +1091,7 @@
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ4" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS4" t="inlineStr">
@@ -1133,11 +1102,6 @@
       <c r="AT4" t="n">
         <v>1</v>
       </c>
-      <c r="AU4" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
-      </c>
       <c r="AV4" t="inlineStr">
         <is>
           <t>jp_weekly</t>
@@ -1251,17 +1215,15 @@
       <c r="O5" t="n">
         <v>1</v>
       </c>
+      <c r="P5" t="n">
+        <v>1</v>
+      </c>
       <c r="Q5" t="n">
         <v>0</v>
       </c>
       <c r="R5" t="n">
         <v>0.0007843961363015203</v>
       </c>
-      <c r="S5" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U5" t="inlineStr">
         <is>
           <t>HOLD_JP_0d0f562527f933882ae5ffa7bbb4</t>
@@ -1269,7 +1231,7 @@
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO5" t="inlineStr">
@@ -1279,12 +1241,7 @@
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ5" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS5" t="inlineStr">
@@ -1295,11 +1252,6 @@
       <c r="AT5" t="n">
         <v>1</v>
       </c>
-      <c r="AU5" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
-      </c>
       <c r="AV5" t="inlineStr">
         <is>
           <t>jp_weekly</t>
@@ -1413,17 +1365,15 @@
       <c r="O6" t="n">
         <v>2</v>
       </c>
+      <c r="P6" t="n">
+        <v>2</v>
+      </c>
       <c r="Q6" t="n">
         <v>0</v>
       </c>
       <c r="R6" t="n">
         <v>0.001568792272603041</v>
       </c>
-      <c r="S6" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U6" t="inlineStr">
         <is>
           <t>HOLD_JP_0d0f562527f933882ae5ffa7bbb4</t>
@@ -1431,7 +1381,7 @@
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO6" t="inlineStr">
@@ -1441,12 +1391,7 @@
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ6" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS6" t="inlineStr">
@@ -1457,11 +1402,6 @@
       <c r="AT6" t="n">
         <v>1</v>
       </c>
-      <c r="AU6" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
-      </c>
       <c r="AV6" t="inlineStr">
         <is>
           <t>jp_weekly</t>
@@ -1575,17 +1515,15 @@
       <c r="O7" t="n">
         <v>1</v>
       </c>
+      <c r="P7" t="n">
+        <v>1</v>
+      </c>
       <c r="Q7" t="n">
         <v>0</v>
       </c>
       <c r="R7" t="n">
         <v>0.0007843961363015203</v>
       </c>
-      <c r="S7" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U7" t="inlineStr">
         <is>
           <t>HOLD_JP_0d0f562527f933882ae5ffa7bbb4</t>
@@ -1593,7 +1531,7 @@
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO7" t="inlineStr">
@@ -1603,12 +1541,7 @@
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ7" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS7" t="inlineStr">
@@ -1619,11 +1552,6 @@
       <c r="AT7" t="n">
         <v>1</v>
       </c>
-      <c r="AU7" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
-      </c>
       <c r="AV7" t="inlineStr">
         <is>
           <t>jp_weekly</t>
@@ -1737,17 +1665,15 @@
       <c r="O8" t="n">
         <v>0</v>
       </c>
+      <c r="P8" t="n">
+        <v>0</v>
+      </c>
       <c r="Q8" t="n">
         <v>0</v>
       </c>
       <c r="R8" t="n">
         <v>0</v>
       </c>
-      <c r="S8" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U8" t="inlineStr">
         <is>
           <t>HOLD_JP_0d0f562527f933882ae5ffa7bbb4</t>
@@ -1755,7 +1681,7 @@
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO8" t="inlineStr">
@@ -1765,12 +1691,7 @@
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ8" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS8" t="inlineStr">
@@ -1781,11 +1702,6 @@
       <c r="AT8" t="n">
         <v>1</v>
       </c>
-      <c r="AU8" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
-      </c>
       <c r="AV8" t="inlineStr">
         <is>
           <t>jp_weekly</t>
@@ -1899,17 +1815,15 @@
       <c r="O9" t="n">
         <v>1</v>
       </c>
+      <c r="P9" t="n">
+        <v>1</v>
+      </c>
       <c r="Q9" t="n">
         <v>0</v>
       </c>
       <c r="R9" t="n">
         <v>0.0007843961363015203</v>
       </c>
-      <c r="S9" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U9" t="inlineStr">
         <is>
           <t>HOLD_JP_0d0f562527f933882ae5ffa7bbb4</t>
@@ -1917,7 +1831,7 @@
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO9" t="inlineStr">
@@ -1927,12 +1841,7 @@
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ9" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS9" t="inlineStr">
@@ -1943,11 +1852,6 @@
       <c r="AT9" t="n">
         <v>1</v>
       </c>
-      <c r="AU9" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
-      </c>
       <c r="AV9" t="inlineStr">
         <is>
           <t>jp_weekly</t>
@@ -2061,17 +1965,15 @@
       <c r="O10" t="n">
         <v>3</v>
       </c>
+      <c r="P10" t="n">
+        <v>3</v>
+      </c>
       <c r="Q10" t="n">
         <v>0</v>
       </c>
       <c r="R10" t="n">
         <v>0.002353188408904561</v>
       </c>
-      <c r="S10" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U10" t="inlineStr">
         <is>
           <t>HOLD_JP_0d0f562527f933882ae5ffa7bbb4</t>
@@ -2079,7 +1981,7 @@
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO10" t="inlineStr">
@@ -2089,12 +1991,7 @@
       </c>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ10" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS10" t="inlineStr">
@@ -2105,11 +2002,6 @@
       <c r="AT10" t="n">
         <v>1</v>
       </c>
-      <c r="AU10" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
-      </c>
       <c r="AV10" t="inlineStr">
         <is>
           <t>jp_weekly</t>
@@ -2223,17 +2115,15 @@
       <c r="O11" t="n">
         <v>0</v>
       </c>
+      <c r="P11" t="n">
+        <v>0</v>
+      </c>
       <c r="Q11" t="n">
         <v>0</v>
       </c>
       <c r="R11" t="n">
         <v>0</v>
       </c>
-      <c r="S11" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U11" t="inlineStr">
         <is>
           <t>HOLD_JP_0d0f562527f933882ae5ffa7bbb4</t>
@@ -2241,7 +2131,7 @@
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO11" t="inlineStr">
@@ -2251,12 +2141,7 @@
       </c>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ11" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS11" t="inlineStr">
@@ -2267,11 +2152,6 @@
       <c r="AT11" t="n">
         <v>1</v>
       </c>
-      <c r="AU11" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
-      </c>
       <c r="AV11" t="inlineStr">
         <is>
           <t>jp_weekly</t>
@@ -2385,17 +2265,15 @@
       <c r="O12" t="n">
         <v>0</v>
       </c>
+      <c r="P12" t="n">
+        <v>0</v>
+      </c>
       <c r="Q12" t="n">
         <v>0</v>
       </c>
       <c r="R12" t="n">
         <v>0</v>
       </c>
-      <c r="S12" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U12" t="inlineStr">
         <is>
           <t>HOLD_JP_0d0f562527f933882ae5ffa7bbb4</t>
@@ -2403,7 +2281,7 @@
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO12" t="inlineStr">
@@ -2413,12 +2291,7 @@
       </c>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ12" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS12" t="inlineStr">
@@ -2429,11 +2302,6 @@
       <c r="AT12" t="n">
         <v>1</v>
       </c>
-      <c r="AU12" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
-      </c>
       <c r="AV12" t="inlineStr">
         <is>
           <t>jp_weekly</t>
@@ -2547,17 +2415,15 @@
       <c r="O13" t="n">
         <v>1</v>
       </c>
+      <c r="P13" t="n">
+        <v>1</v>
+      </c>
       <c r="Q13" t="n">
         <v>0</v>
       </c>
       <c r="R13" t="n">
         <v>0.0007843961363015203</v>
       </c>
-      <c r="S13" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U13" t="inlineStr">
         <is>
           <t>HOLD_JP_0d0f562527f933882ae5ffa7bbb4</t>
@@ -2565,7 +2431,7 @@
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO13" t="inlineStr">
@@ -2575,12 +2441,7 @@
       </c>
       <c r="AP13" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ13" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS13" t="inlineStr">
@@ -2591,11 +2452,6 @@
       <c r="AT13" t="n">
         <v>1</v>
       </c>
-      <c r="AU13" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
-      </c>
       <c r="AV13" t="inlineStr">
         <is>
           <t>jp_weekly</t>
@@ -2709,17 +2565,15 @@
       <c r="O14" t="n">
         <v>2</v>
       </c>
+      <c r="P14" t="n">
+        <v>2</v>
+      </c>
       <c r="Q14" t="n">
         <v>0</v>
       </c>
       <c r="R14" t="n">
         <v>0.001568792272603041</v>
       </c>
-      <c r="S14" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U14" t="inlineStr">
         <is>
           <t>HOLD_JP_0d0f562527f933882ae5ffa7bbb4</t>
@@ -2727,7 +2581,7 @@
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO14" t="inlineStr">
@@ -2737,12 +2591,7 @@
       </c>
       <c r="AP14" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ14" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS14" t="inlineStr">
@@ -2753,11 +2602,6 @@
       <c r="AT14" t="n">
         <v>1</v>
       </c>
-      <c r="AU14" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
-      </c>
       <c r="AV14" t="inlineStr">
         <is>
           <t>jp_weekly</t>
@@ -2871,17 +2715,15 @@
       <c r="O15" t="n">
         <v>3</v>
       </c>
+      <c r="P15" t="n">
+        <v>3</v>
+      </c>
       <c r="Q15" t="n">
         <v>0</v>
       </c>
       <c r="R15" t="n">
         <v>0.002353188408904561</v>
       </c>
-      <c r="S15" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U15" t="inlineStr">
         <is>
           <t>HOLD_JP_0d0f562527f933882ae5ffa7bbb4</t>
@@ -2889,7 +2731,7 @@
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO15" t="inlineStr">
@@ -2899,12 +2741,7 @@
       </c>
       <c r="AP15" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ15" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS15" t="inlineStr">
@@ -2915,11 +2752,6 @@
       <c r="AT15" t="n">
         <v>1</v>
       </c>
-      <c r="AU15" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
-      </c>
       <c r="AV15" t="inlineStr">
         <is>
           <t>jp_weekly</t>
@@ -3033,17 +2865,15 @@
       <c r="O16" t="n">
         <v>1</v>
       </c>
+      <c r="P16" t="n">
+        <v>1</v>
+      </c>
       <c r="Q16" t="n">
         <v>0</v>
       </c>
       <c r="R16" t="n">
         <v>0.0007843961363015203</v>
       </c>
-      <c r="S16" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U16" t="inlineStr">
         <is>
           <t>HOLD_JP_0d0f562527f933882ae5ffa7bbb4</t>
@@ -3051,7 +2881,7 @@
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO16" t="inlineStr">
@@ -3061,12 +2891,7 @@
       </c>
       <c r="AP16" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ16" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS16" t="inlineStr">
@@ -3076,11 +2901,6 @@
       </c>
       <c r="AT16" t="n">
         <v>1</v>
-      </c>
-      <c r="AU16" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV16" t="inlineStr">
         <is>
